--- a/results/tables/net_stats.xlsx
+++ b/results/tables/net_stats.xlsx
@@ -1,146 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10308"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://radbouduniversiteit-my.sharepoint.com/personal/jos_slabbekoorn_ru_nl/Documents/project - network/results/tables/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_4364FDDE8F79A8D366075C52F37BD272BAC7AEF1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0576412B-DE3F-BF45-B7D8-D926B011AA95}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="780" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
-  <si>
-    <t>statistic</t>
-  </si>
-  <si>
-    <t>first_all_observed</t>
-  </si>
-  <si>
-    <t>first_sen_observed</t>
-  </si>
-  <si>
-    <t>last_all_observed</t>
-  </si>
-  <si>
-    <t>last_sen_observed</t>
-  </si>
-  <si>
-    <t>all_all_observed</t>
-  </si>
-  <si>
-    <t>all_sen_observed</t>
-  </si>
-  <si>
-    <t>N nodes total</t>
-  </si>
-  <si>
-    <t>N nodes excluding isolates</t>
-  </si>
-  <si>
-    <t>density</t>
-  </si>
-  <si>
-    <t>clustering coefficient</t>
-  </si>
-  <si>
-    <t>average betweenness centrality</t>
-  </si>
-  <si>
-    <t>mean path distance</t>
-  </si>
-  <si>
-    <t>Jaccard's Index (period 1 - 2)</t>
-  </si>
-  <si>
-    <t>gender Moran's I (nb distance 1)</t>
-  </si>
-  <si>
-    <t>gender Moran's I (nb distance 2)</t>
-  </si>
-  <si>
-    <t>discipline Moran's I (nb distance 1)</t>
-  </si>
-  <si>
-    <t>discipline Moran's I (nb distance 2)</t>
-  </si>
-  <si>
-    <t>uni22p__eur Moran's I (nb distance 1 )</t>
-  </si>
-  <si>
-    <t>uni22p__eur Moran's I (nb distance 2 )</t>
-  </si>
-  <si>
-    <t>uni22p__ru Moran's I (nb distance 1 )</t>
-  </si>
-  <si>
-    <t>uni22p__ru Moran's I (nb distance 2 )</t>
-  </si>
-  <si>
-    <t>uni22p__ul Moran's I (nb distance 1 )</t>
-  </si>
-  <si>
-    <t>uni22p__ul Moran's I (nb distance 2 )</t>
-  </si>
-  <si>
-    <t>uni22p__uu Moran's I (nb distance 1 )</t>
-  </si>
-  <si>
-    <t>uni22p__uu Moran's I (nb distance 2 )</t>
-  </si>
-  <si>
-    <t>uni22p__uva Moran's I (nb distance 1 )</t>
-  </si>
-  <si>
-    <t>uni22p__uva Moran's I (nb distance 2 )</t>
-  </si>
-  <si>
-    <t>uni22p__uvg Moran's I (nb distance 1 )</t>
-  </si>
-  <si>
-    <t>uni22p__uvg Moran's I (nb distance 2 )</t>
-  </si>
-  <si>
-    <t>uni22p__uvt Moran's I (nb distance 1 )</t>
-  </si>
-  <si>
-    <t>uni22p__uvt Moran's I (nb distance 2 )</t>
-  </si>
-  <si>
-    <t>uni22p__vu Moran's I (nb distance 1 )</t>
-  </si>
-  <si>
-    <t>uni22p__vu Moran's I (nb distance 2 )</t>
-  </si>
-  <si>
-    <t>full prof Moran's I (nb distance 1)</t>
-  </si>
-  <si>
-    <t>full prof Moran's I (nb distance 2)</t>
-  </si>
-  <si>
-    <t>I index Moran's I (nb distance 1)</t>
-  </si>
-  <si>
-    <t>I index Moran's I (nb distance 2)</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -188,21 +63,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -240,7 +107,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -274,7 +141,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -309,10 +175,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -485,45 +350,52 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G30"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>7</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>statistic</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>first_all_observed</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>first_sen_observed</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>last_all_observed</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>last_sen_observed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>all_all_observed</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>all_sen_observed</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>N nodes total</t>
+        </is>
       </c>
       <c r="B2">
         <v>1175</v>
@@ -544,694 +416,704 @@
         <v>902</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>8</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>N nodes excluding isolates</t>
+        </is>
       </c>
       <c r="B3">
-        <v>393</v>
+        <v>309</v>
       </c>
       <c r="C3">
-        <v>269</v>
+        <v>198</v>
       </c>
       <c r="D3">
-        <v>384</v>
+        <v>295</v>
       </c>
       <c r="E3">
-        <v>274</v>
+        <v>212</v>
       </c>
       <c r="F3">
-        <v>431</v>
+        <v>351</v>
       </c>
       <c r="G3">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>9</v>
+        <v>251</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>density</t>
+        </is>
       </c>
       <c r="B4">
-        <v>3.8203631882271919E-4</v>
+        <v>0.0002457501178005727</v>
       </c>
       <c r="C4">
-        <v>4.0605289515714248E-4</v>
+        <v>0.0002239443239957574</v>
       </c>
       <c r="D4">
-        <v>3.7406212620972131E-4</v>
+        <v>0.0002399507049911197</v>
       </c>
       <c r="E4">
-        <v>4.7495884100199091E-4</v>
+        <v>0.0002866979532473158</v>
       </c>
       <c r="F4">
-        <v>9.4820399434557246E-4</v>
+        <v>0.000672731885896553</v>
       </c>
       <c r="G4">
-        <v>1.092651426968311E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>10</v>
+        <v>0.0007259733580082244</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>clustering coefficient</t>
+        </is>
       </c>
       <c r="B5">
-        <v>0.15915697674418611</v>
+        <v>0.1274787535410765</v>
       </c>
       <c r="C5">
-        <v>0.18421052631578949</v>
+        <v>0.1931330472103004</v>
       </c>
       <c r="D5">
-        <v>0.15019255455712449</v>
+        <v>0.1380597014925373</v>
       </c>
       <c r="E5">
-        <v>0.20837927232635059</v>
+        <v>0.2101449275362319</v>
       </c>
       <c r="F5">
-        <v>0.25529767911200812</v>
+        <v>0.2894248608534323</v>
       </c>
       <c r="G5">
-        <v>0.28606811145510841</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>11</v>
+        <v>0.3204272363150868</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>average betweenness centrality</t>
+        </is>
       </c>
       <c r="B6">
-        <v>5.4551808257717479E-6</v>
+        <v>5.376693461449443E-07</v>
       </c>
       <c r="C6">
-        <v>3.211509261697395E-6</v>
+        <v>2.269521232191444E-07</v>
       </c>
       <c r="D6">
-        <v>1.468022718198504E-5</v>
+        <v>1.397940299976843E-06</v>
       </c>
       <c r="E6">
-        <v>1.818624784976532E-5</v>
+        <v>1.341205017337229E-06</v>
       </c>
       <c r="F6">
-        <v>3.9083122970201643E-4</v>
+        <v>0.0001429483568284019</v>
       </c>
       <c r="G6">
-        <v>3.2728957094837861E-4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>12</v>
+        <v>0.0001629270152049723</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>mean path distance</t>
+        </is>
       </c>
       <c r="B7">
-        <v>4.1070045758535727</v>
+        <v>2.147757255936675</v>
       </c>
       <c r="C7">
-        <v>2.9822784810126581</v>
+        <v>1.549668874172185</v>
       </c>
       <c r="D7">
-        <v>5.0418580908626849</v>
+        <v>2.920203735144312</v>
       </c>
       <c r="E7">
-        <v>4.8169296987087522</v>
+        <v>2.466367713004484</v>
       </c>
       <c r="F7">
-        <v>6.709041996172318</v>
+        <v>6.12006375066407</v>
       </c>
       <c r="G7">
-        <v>6.1446316513367147</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>13</v>
+        <v>6.720526113671275</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Jaccard's Index (period 1 - 2)</t>
+        </is>
       </c>
       <c r="B8">
-        <v>0.20399999999999999</v>
+        <v>0.208092485549133</v>
       </c>
       <c r="C8">
-        <v>0.14385150812064959</v>
+        <v>0.1584905660377358</v>
       </c>
       <c r="D8">
-        <v>0.21892655367231639</v>
+        <v>0.208502024291498</v>
       </c>
       <c r="E8">
-        <v>0.21782178217821779</v>
+        <v>0.2017804154302671</v>
       </c>
       <c r="F8">
-        <v>0.29463307776560788</v>
+        <v>0.2872023809523809</v>
       </c>
       <c r="G8">
-        <v>0.27164685908319192</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>14</v>
+        <v>0.2705314009661836</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>gender Moran's I (nb distance 1)</t>
+        </is>
       </c>
       <c r="B9">
-        <v>0.17203521440713729</v>
+        <v>0.1636476417901848</v>
       </c>
       <c r="C9">
-        <v>0.11553588845648879</v>
+        <v>0.1105877947582054</v>
       </c>
       <c r="D9">
-        <v>0.1852750921135439</v>
+        <v>0.157400862373645</v>
       </c>
       <c r="E9">
-        <v>0.19173486344292789</v>
+        <v>0.1887244135658444</v>
       </c>
       <c r="F9">
-        <v>0.14424986709114229</v>
+        <v>0.09443592663896917</v>
       </c>
       <c r="G9">
-        <v>0.11832863006672779</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>15</v>
+        <v>0.08146690498122129</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>gender Moran's I (nb distance 2)</t>
+        </is>
       </c>
       <c r="B10">
-        <v>1.1628479050426381E-2</v>
+        <v>-0.003565287256088266</v>
       </c>
       <c r="C10">
-        <v>-3.8719008536629761E-2</v>
+        <v>-0.1207432754761292</v>
       </c>
       <c r="D10">
-        <v>7.0507953748343011E-4</v>
+        <v>0.03907670755765679</v>
       </c>
       <c r="E10">
-        <v>-3.1416558910895052E-4</v>
+        <v>-0.02738413249903852</v>
       </c>
       <c r="F10">
-        <v>-8.0960381023369842E-3</v>
+        <v>0.067773078221461</v>
       </c>
       <c r="G10">
-        <v>-1.8267847672796891E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>16</v>
+        <v>0.04779488207015987</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>discipline Moran's I (nb distance 1)</t>
+        </is>
       </c>
       <c r="B11">
-        <v>0.74103268451059878</v>
+        <v>0.7278560337630041</v>
       </c>
       <c r="C11">
-        <v>0.75986881165639397</v>
+        <v>0.7770497659474028</v>
       </c>
       <c r="D11">
-        <v>0.76796201042978529</v>
+        <v>0.7104742207214704</v>
       </c>
       <c r="E11">
-        <v>0.786071844128306</v>
+        <v>0.7564478264055619</v>
       </c>
       <c r="F11">
-        <v>0.74619516406395769</v>
+        <v>0.715174710635651</v>
       </c>
       <c r="G11">
-        <v>0.76657309497135462</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>17</v>
+        <v>0.7514381957007837</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>discipline Moran's I (nb distance 2)</t>
+        </is>
       </c>
       <c r="B12">
-        <v>0.65191426164066124</v>
+        <v>0.7461267152148062</v>
       </c>
       <c r="C12">
-        <v>0.71554112035053141</v>
+        <v>0.871773749985834</v>
       </c>
       <c r="D12">
-        <v>0.71394377372956719</v>
+        <v>0.6445511234521119</v>
       </c>
       <c r="E12">
-        <v>0.7763438690390817</v>
+        <v>0.7345786015587612</v>
       </c>
       <c r="F12">
-        <v>0.64785410499406282</v>
+        <v>0.6466148407539208</v>
       </c>
       <c r="G12">
-        <v>0.68558834340490582</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>18</v>
+        <v>0.7011002667908954</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>uni22p__eur Moran's I (nb distance 1 )</t>
+        </is>
       </c>
       <c r="B13">
-        <v>1.199099939975987</v>
+        <v>1.539368958109556</v>
       </c>
       <c r="C13">
-        <v>0.83623975605107026</v>
+        <v>1.007542515989194</v>
       </c>
       <c r="D13">
-        <v>1.0960333133253299</v>
+        <v>1.006018282312921</v>
       </c>
       <c r="E13">
-        <v>1.078069602758476</v>
+        <v>1.045896702877826</v>
       </c>
       <c r="F13">
-        <v>1.194613215388193</v>
+        <v>1.273935860058307</v>
       </c>
       <c r="G13">
-        <v>0.9655160362300873</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>19</v>
+        <v>0.8342147894034656</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>uni22p__eur Moran's I (nb distance 2 )</t>
+        </is>
       </c>
       <c r="B14">
-        <v>0.18091570914079869</v>
+        <v>0.177590702947845</v>
       </c>
       <c r="C14">
-        <v>-1.3325796559072711E-2</v>
+        <v>0.01954177897574098</v>
       </c>
       <c r="D14">
-        <v>0.4513976007421811</v>
+        <v>0.297542499897342</v>
       </c>
       <c r="E14">
-        <v>0.14022147198247639</v>
+        <v>0.22120850666719</v>
       </c>
       <c r="F14">
-        <v>0.70070914426346431</v>
+        <v>0.6006572831732891</v>
       </c>
       <c r="G14">
-        <v>0.1868780097754511</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>20</v>
+        <v>0.120958590724051</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>uni22p__ru Moran's I (nb distance 1 )</t>
+        </is>
       </c>
       <c r="B15">
-        <v>0.85801929789794873</v>
+        <v>0.8361472156680747</v>
       </c>
       <c r="C15">
-        <v>0.86762325239147176</v>
+        <v>0.7923215554672988</v>
       </c>
       <c r="D15">
-        <v>0.74672704848387228</v>
+        <v>0.7244824019916242</v>
       </c>
       <c r="E15">
-        <v>0.75235732702194358</v>
+        <v>0.7223190426397195</v>
       </c>
       <c r="F15">
-        <v>0.83854820038362221</v>
+        <v>0.8370837189501242</v>
       </c>
       <c r="G15">
-        <v>0.78171733003218402</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>21</v>
+        <v>0.7886846477154247</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>uni22p__ru Moran's I (nb distance 2 )</t>
+        </is>
       </c>
       <c r="B16">
-        <v>0.82872729034603088</v>
+        <v>1.03520893918016</v>
       </c>
       <c r="C16">
-        <v>0.76651850342200967</v>
+        <v>0.2864722512683497</v>
       </c>
       <c r="D16">
-        <v>0.62378492166499522</v>
+        <v>0.7248782667500093</v>
       </c>
       <c r="E16">
-        <v>0.65239943337713202</v>
+        <v>0.7364174308802443</v>
       </c>
       <c r="F16">
-        <v>0.7651137745705614</v>
+        <v>0.7942633524984383</v>
       </c>
       <c r="G16">
-        <v>0.54299373892509584</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>22</v>
+        <v>0.6646921160670921</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>uni22p__ul Moran's I (nb distance 1 )</t>
+        </is>
       </c>
       <c r="B17">
-        <v>0.50491602860474916</v>
+        <v>0.4595968085772847</v>
       </c>
       <c r="C17">
-        <v>0.58032634032634067</v>
+        <v>0.5402835751672964</v>
       </c>
       <c r="D17">
-        <v>0.64343916365069997</v>
+        <v>0.4735449754652804</v>
       </c>
       <c r="E17">
-        <v>0.56595505886286113</v>
+        <v>0.4267201933868605</v>
       </c>
       <c r="F17">
-        <v>0.5174030443366856</v>
+        <v>0.4442640312418263</v>
       </c>
       <c r="G17">
-        <v>0.54355195411229951</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>23</v>
+        <v>0.4401455741661943</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>uni22p__ul Moran's I (nb distance 2 )</t>
+        </is>
       </c>
       <c r="B18">
-        <v>0.43963109363253289</v>
+        <v>0.3065759801786578</v>
       </c>
       <c r="C18">
-        <v>0.55663717595535689</v>
+        <v>0.465833549166882</v>
       </c>
       <c r="D18">
-        <v>0.56921703336585749</v>
+        <v>0.3166282325642773</v>
       </c>
       <c r="E18">
-        <v>0.49687760798871861</v>
+        <v>0.3191299972909167</v>
       </c>
       <c r="F18">
-        <v>0.35748572438313342</v>
+        <v>0.238934769625482</v>
       </c>
       <c r="G18">
-        <v>0.43180908448272992</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>24</v>
+        <v>0.2903216253910705</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>uni22p__uu Moran's I (nb distance 1 )</t>
+        </is>
       </c>
       <c r="B19">
-        <v>1.1092544762058989</v>
+        <v>1.41148297152787</v>
       </c>
       <c r="C19">
-        <v>1.152000653274543</v>
+        <v>1.558177515961555</v>
       </c>
       <c r="D19">
-        <v>0.84239307655662776</v>
+        <v>1.035639544676203</v>
       </c>
       <c r="E19">
-        <v>0.85864859042119379</v>
+        <v>0.9740601012575597</v>
       </c>
       <c r="F19">
-        <v>0.96577743502500213</v>
+        <v>1.200584962664583</v>
       </c>
       <c r="G19">
-        <v>0.90665596617083022</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>25</v>
+        <v>1.13939065071773</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>uni22p__uu Moran's I (nb distance 2 )</t>
+        </is>
       </c>
       <c r="B20">
-        <v>0.72742963485257328</v>
+        <v>0.9404565402502209</v>
       </c>
       <c r="C20">
-        <v>0.97853636584094472</v>
+        <v>1.763790703281162</v>
       </c>
       <c r="D20">
-        <v>0.69594547497203429</v>
+        <v>0.6871195190399672</v>
       </c>
       <c r="E20">
-        <v>0.61452494916483458</v>
+        <v>0.406542319237248</v>
       </c>
       <c r="F20">
-        <v>0.6187961781007687</v>
+        <v>0.8387877144917548</v>
       </c>
       <c r="G20">
-        <v>0.61885512665418441</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>26</v>
+        <v>0.7349504687780996</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>uni22p__uva Moran's I (nb distance 1 )</t>
+        </is>
       </c>
       <c r="B21">
-        <v>0.63052425397827772</v>
+        <v>0.5999581443901493</v>
       </c>
       <c r="C21">
-        <v>0.56931751677254583</v>
+        <v>0.6170544468419092</v>
       </c>
       <c r="D21">
-        <v>0.69741467480509811</v>
+        <v>0.5334819581548905</v>
       </c>
       <c r="E21">
-        <v>0.60928854783658226</v>
+        <v>0.535008326309083</v>
       </c>
       <c r="F21">
-        <v>0.69473523338983023</v>
+        <v>0.6269310587521604</v>
       </c>
       <c r="G21">
-        <v>0.62895434396410799</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>27</v>
+        <v>0.5955227668289209</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>uni22p__uva Moran's I (nb distance 2 )</t>
+        </is>
       </c>
       <c r="B22">
-        <v>0.44058635129307111</v>
+        <v>0.5697136128652364</v>
       </c>
       <c r="C22">
-        <v>0.28883064418158377</v>
+        <v>0.4538092986418497</v>
       </c>
       <c r="D22">
-        <v>0.45780085386469682</v>
+        <v>0.2196776215104349</v>
       </c>
       <c r="E22">
-        <v>0.32762724992274261</v>
+        <v>0.1533600503052278</v>
       </c>
       <c r="F22">
-        <v>0.52014060820991459</v>
+        <v>0.3612302884435364</v>
       </c>
       <c r="G22">
-        <v>0.43393381882625331</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>28</v>
+        <v>0.2580910369955698</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>uni22p__uvg Moran's I (nb distance 1 )</t>
+        </is>
       </c>
       <c r="B23">
-        <v>1.181075079604492</v>
+        <v>1.088537761783374</v>
       </c>
       <c r="C23">
-        <v>0.97023790081115258</v>
+        <v>0.5735180732958894</v>
       </c>
       <c r="D23">
-        <v>0.82800300104092417</v>
+        <v>0.961608923483921</v>
       </c>
       <c r="E23">
-        <v>1.0634248000422351</v>
+        <v>1.225367466927984</v>
       </c>
       <c r="F23">
-        <v>1.105970062061046</v>
+        <v>1.138269230769236</v>
       </c>
       <c r="G23">
-        <v>1.0199321141557089</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>29</v>
+        <v>1.147987729214342</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>uni22p__uvg Moran's I (nb distance 2 )</t>
+        </is>
       </c>
       <c r="B24">
-        <v>1.2362107663578259</v>
+        <v>0.8004510921177566</v>
       </c>
       <c r="C24">
-        <v>1.2559361599604859</v>
+        <v>0.01061571125265402</v>
       </c>
       <c r="D24">
-        <v>1.016355689597942</v>
+        <v>1.107754002648363</v>
       </c>
       <c r="E24">
-        <v>1.331889713259145</v>
+        <v>1.458181982012431</v>
       </c>
       <c r="F24">
-        <v>1.052963247776328</v>
+        <v>1.191514736442728</v>
       </c>
       <c r="G24">
-        <v>0.90733997502402608</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>30</v>
+        <v>1.305239166206532</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>uni22p__uvt Moran's I (nb distance 1 )</t>
+        </is>
       </c>
       <c r="B25">
-        <v>0.38994739359158609</v>
+        <v>0.4227000427899048</v>
       </c>
       <c r="C25">
-        <v>0.45300646323373589</v>
+        <v>0.4549899096674994</v>
       </c>
       <c r="D25">
-        <v>0.79448166326864911</v>
+        <v>0.8739972899729066</v>
       </c>
       <c r="E25">
-        <v>0.96765114318305678</v>
+        <v>1.200867768595039</v>
       </c>
       <c r="F25">
-        <v>0.5400162020905992</v>
+        <v>0.6512090592334572</v>
       </c>
       <c r="G25">
-        <v>0.68509929366610156</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>31</v>
+        <v>0.8219821708282342</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>uni22p__uvt Moran's I (nb distance 2 )</t>
+        </is>
       </c>
       <c r="B26">
-        <v>0.1034463346314143</v>
+        <v>0.03739837398374005</v>
       </c>
       <c r="C26">
-        <v>0.16414802718568619</v>
+        <v>0.1934429207156478</v>
       </c>
       <c r="D26">
-        <v>0.54628821249158788</v>
+        <v>0.8961647936398941</v>
       </c>
       <c r="E26">
-        <v>0.7475766026902344</v>
+        <v>1.265495867768591</v>
       </c>
       <c r="F26">
-        <v>0.25208370264804991</v>
+        <v>0.3756629120136186</v>
       </c>
       <c r="G26">
-        <v>0.43143771519654223</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>32</v>
+        <v>0.6575291225504258</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>uni22p__vu Moran's I (nb distance 1 )</t>
+        </is>
       </c>
       <c r="B27">
-        <v>0.80708973370841841</v>
+        <v>0.8684858002341316</v>
       </c>
       <c r="C27">
-        <v>0.7710604385480061</v>
+        <v>0.9013459832619916</v>
       </c>
       <c r="D27">
-        <v>0.75194850961806925</v>
+        <v>0.8124858428853279</v>
       </c>
       <c r="E27">
-        <v>0.72041780851456383</v>
+        <v>0.7726540906578282</v>
       </c>
       <c r="F27">
-        <v>0.76714843668815491</v>
+        <v>0.7555695972126655</v>
       </c>
       <c r="G27">
-        <v>0.70421457837020618</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>33</v>
+        <v>0.7057414103594334</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>uni22p__vu Moran's I (nb distance 2 )</t>
+        </is>
       </c>
       <c r="B28">
-        <v>0.65961530799663304</v>
+        <v>0.616364973671029</v>
       </c>
       <c r="C28">
-        <v>0.49256715161566289</v>
+        <v>0.6022664455500317</v>
       </c>
       <c r="D28">
-        <v>0.46849503583030822</v>
+        <v>0.5456127943384335</v>
       </c>
       <c r="E28">
-        <v>0.44843155508578791</v>
+        <v>0.468129896494542</v>
       </c>
       <c r="F28">
-        <v>0.59102975565200977</v>
+        <v>0.6152156668309717</v>
       </c>
       <c r="G28">
-        <v>0.47989864141283339</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>34</v>
+        <v>0.4520751369731327</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>full prof Moran's I (nb distance 1)</t>
+        </is>
       </c>
       <c r="B29">
-        <v>-0.20295214494467129</v>
+        <v>-0.2199627796220964</v>
       </c>
       <c r="C29">
-        <v>-0.1967865444214861</v>
+        <v>-0.07389166506502601</v>
       </c>
       <c r="D29">
-        <v>2.2952473304585969E-2</v>
+        <v>0.1829652137217497</v>
       </c>
       <c r="E29">
-        <v>-4.2800793057683313E-2</v>
+        <v>0.1299078959235203</v>
       </c>
       <c r="F29">
-        <v>-0.13790385079452711</v>
+        <v>-0.1336055205933237</v>
       </c>
       <c r="G29">
-        <v>-9.5074536642270835E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>35</v>
+        <v>-0.02348838966317501</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>full prof Moran's I (nb distance 2)</t>
+        </is>
       </c>
       <c r="B30">
-        <v>-5.2243103160984163E-2</v>
+        <v>0.06091150733694803</v>
       </c>
       <c r="C30">
-        <v>-6.8963969009568277E-2</v>
+        <v>0.1250152874797757</v>
       </c>
       <c r="D30">
-        <v>5.4950662198806621E-2</v>
+        <v>-0.0459965060161504</v>
       </c>
       <c r="E30">
-        <v>9.7216274149902152E-2</v>
+        <v>0.01376829125898488</v>
       </c>
       <c r="F30">
-        <v>-1.172259273770641E-2</v>
+        <v>-0.05875493411882184</v>
       </c>
       <c r="G30">
-        <v>-1.0253097736670909E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>36</v>
-      </c>
-      <c r="B31">
-        <v>0.139211565093219</v>
-      </c>
-      <c r="C31">
-        <v>0.2928955384750988</v>
-      </c>
-      <c r="D31">
-        <v>0.33947915229871489</v>
-      </c>
-      <c r="E31">
-        <v>0.33828581007554948</v>
-      </c>
-      <c r="F31">
-        <v>8.2715139602652712E-2</v>
-      </c>
-      <c r="G31">
-        <v>0.24152839395030959</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32">
-        <v>0.41096128293078538</v>
-      </c>
-      <c r="C32">
-        <v>0.57844481857605168</v>
-      </c>
-      <c r="D32">
-        <v>0.37671274619842537</v>
-      </c>
-      <c r="E32">
-        <v>0.46534187383066788</v>
-      </c>
-      <c r="F32">
-        <v>0.14084227671573021</v>
-      </c>
-      <c r="G32">
-        <v>0.2267035092764445</v>
+        <v>-0.08010649247973618</v>
       </c>
     </row>
   </sheetData>

--- a/results/tables/net_stats.xlsx
+++ b/results/tables/net_stats.xlsx
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.1636476417901848</v>
+        <v>0.06877423324916887</v>
       </c>
       <c r="C9">
-        <v>0.1105877947582054</v>
+        <v>0.04085724199938107</v>
       </c>
       <c r="D9">
-        <v>0.157400862373645</v>
+        <v>0.05679533721901837</v>
       </c>
       <c r="E9">
-        <v>0.1887244135658444</v>
+        <v>0.07195682772815663</v>
       </c>
       <c r="F9">
-        <v>0.09443592663896917</v>
+        <v>0.05167299458233638</v>
       </c>
       <c r="G9">
-        <v>0.08146690498122129</v>
+        <v>0.04311213596339497</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
-        <v>-0.003565287256088266</v>
+        <v>0.06877423324916887</v>
       </c>
       <c r="C10">
-        <v>-0.1207432754761292</v>
+        <v>0.04085724199938107</v>
       </c>
       <c r="D10">
-        <v>0.03907670755765679</v>
+        <v>0.05679533721901837</v>
       </c>
       <c r="E10">
-        <v>-0.02738413249903852</v>
+        <v>0.07195682772815663</v>
       </c>
       <c r="F10">
-        <v>0.067773078221461</v>
+        <v>0.05167299458233638</v>
       </c>
       <c r="G10">
-        <v>0.04779488207015987</v>
+        <v>0.04311213596339497</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.7278560337630041</v>
+        <v>0.3356595512779528</v>
       </c>
       <c r="C11">
-        <v>0.7770497659474028</v>
+        <v>0.299251805250051</v>
       </c>
       <c r="D11">
-        <v>0.7104742207214704</v>
+        <v>0.2783668179117221</v>
       </c>
       <c r="E11">
-        <v>0.7564478264055619</v>
+        <v>0.3033982852282111</v>
       </c>
       <c r="F11">
-        <v>0.715174710635651</v>
+        <v>0.4277102585715828</v>
       </c>
       <c r="G11">
-        <v>0.7514381957007837</v>
+        <v>0.4201679462346051</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.7461267152148062</v>
+        <v>0.3356595512779528</v>
       </c>
       <c r="C12">
-        <v>0.871773749985834</v>
+        <v>0.299251805250051</v>
       </c>
       <c r="D12">
-        <v>0.6445511234521119</v>
+        <v>0.2783668179117221</v>
       </c>
       <c r="E12">
-        <v>0.7345786015587612</v>
+        <v>0.3033982852282111</v>
       </c>
       <c r="F12">
-        <v>0.6466148407539208</v>
+        <v>0.4277102585715828</v>
       </c>
       <c r="G12">
-        <v>0.7011002667908954</v>
+        <v>0.4201679462346051</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
-        <v>1.539368958109556</v>
+        <v>0.5437984479509115</v>
       </c>
       <c r="C13">
-        <v>1.007542515989194</v>
+        <v>0.3490362996748443</v>
       </c>
       <c r="D13">
-        <v>1.006018282312921</v>
+        <v>0.340908586650942</v>
       </c>
       <c r="E13">
-        <v>1.045896702877826</v>
+        <v>0.3968700163625857</v>
       </c>
       <c r="F13">
-        <v>1.273935860058307</v>
+        <v>0.6070383226980913</v>
       </c>
       <c r="G13">
-        <v>0.8342147894034656</v>
+        <v>0.4350030639277364</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.177590702947845</v>
+        <v>0.5437984479509115</v>
       </c>
       <c r="C14">
-        <v>0.01954177897574098</v>
+        <v>0.3490362996748443</v>
       </c>
       <c r="D14">
-        <v>0.297542499897342</v>
+        <v>0.340908586650942</v>
       </c>
       <c r="E14">
-        <v>0.22120850666719</v>
+        <v>0.3968700163625857</v>
       </c>
       <c r="F14">
-        <v>0.6006572831732891</v>
+        <v>0.6070383226980913</v>
       </c>
       <c r="G14">
-        <v>0.120958590724051</v>
+        <v>0.4350030639277364</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.8361472156680747</v>
+        <v>0.3598924451242705</v>
       </c>
       <c r="C15">
-        <v>0.7923215554672988</v>
+        <v>0.3197700729898394</v>
       </c>
       <c r="D15">
-        <v>0.7244824019916242</v>
+        <v>0.2808271542058434</v>
       </c>
       <c r="E15">
-        <v>0.7223190426397195</v>
+        <v>0.3220797572643257</v>
       </c>
       <c r="F15">
-        <v>0.8370837189501242</v>
+        <v>0.477435282919582</v>
       </c>
       <c r="G15">
-        <v>0.7886846477154247</v>
+        <v>0.483345962495499</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
-        <v>1.03520893918016</v>
+        <v>0.3598924451242705</v>
       </c>
       <c r="C16">
-        <v>0.2864722512683497</v>
+        <v>0.3197700729898394</v>
       </c>
       <c r="D16">
-        <v>0.7248782667500093</v>
+        <v>0.2808271542058434</v>
       </c>
       <c r="E16">
-        <v>0.7364174308802443</v>
+        <v>0.3220797572643257</v>
       </c>
       <c r="F16">
-        <v>0.7942633524984383</v>
+        <v>0.477435282919582</v>
       </c>
       <c r="G16">
-        <v>0.6646921160670921</v>
+        <v>0.483345962495499</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.4595968085772847</v>
+        <v>0.3086103539957364</v>
       </c>
       <c r="C17">
-        <v>0.5402835751672964</v>
+        <v>0.2871506179033356</v>
       </c>
       <c r="D17">
-        <v>0.4735449754652804</v>
+        <v>0.2318296572425316</v>
       </c>
       <c r="E17">
-        <v>0.4267201933868605</v>
+        <v>0.2463553210147415</v>
       </c>
       <c r="F17">
-        <v>0.4442640312418263</v>
+        <v>0.3668229262027056</v>
       </c>
       <c r="G17">
-        <v>0.4401455741661943</v>
+        <v>0.3612123476476142</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
-        <v>0.3065759801786578</v>
+        <v>0.3086103539957364</v>
       </c>
       <c r="C18">
-        <v>0.465833549166882</v>
+        <v>0.2871506179033356</v>
       </c>
       <c r="D18">
-        <v>0.3166282325642773</v>
+        <v>0.2318296572425316</v>
       </c>
       <c r="E18">
-        <v>0.3191299972909167</v>
+        <v>0.2463553210147415</v>
       </c>
       <c r="F18">
-        <v>0.238934769625482</v>
+        <v>0.3668229262027056</v>
       </c>
       <c r="G18">
-        <v>0.2903216253910705</v>
+        <v>0.3612123476476142</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
-        <v>1.41148297152787</v>
+        <v>0.5248293166701731</v>
       </c>
       <c r="C19">
-        <v>1.558177515961555</v>
+        <v>0.4841127073549646</v>
       </c>
       <c r="D19">
-        <v>1.035639544676203</v>
+        <v>0.3227570079987112</v>
       </c>
       <c r="E19">
-        <v>0.9740601012575597</v>
+        <v>0.3646585951206311</v>
       </c>
       <c r="F19">
-        <v>1.200584962664583</v>
+        <v>0.6068659939641238</v>
       </c>
       <c r="G19">
-        <v>1.13939065071773</v>
+        <v>0.586502107420562</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
-        <v>0.9404565402502209</v>
+        <v>0.5248293166701731</v>
       </c>
       <c r="C20">
-        <v>1.763790703281162</v>
+        <v>0.4841127073549646</v>
       </c>
       <c r="D20">
-        <v>0.6871195190399672</v>
+        <v>0.3227570079987112</v>
       </c>
       <c r="E20">
-        <v>0.406542319237248</v>
+        <v>0.3646585951206311</v>
       </c>
       <c r="F20">
-        <v>0.8387877144917548</v>
+        <v>0.6068659939641238</v>
       </c>
       <c r="G20">
-        <v>0.7349504687780996</v>
+        <v>0.586502107420562</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.5999581443901493</v>
+        <v>0.3204598294937268</v>
       </c>
       <c r="C21">
-        <v>0.6170544468419092</v>
+        <v>0.2785680359787788</v>
       </c>
       <c r="D21">
-        <v>0.5334819581548905</v>
+        <v>0.2306258404797179</v>
       </c>
       <c r="E21">
-        <v>0.535008326309083</v>
+        <v>0.2588043636512737</v>
       </c>
       <c r="F21">
-        <v>0.6269310587521604</v>
+        <v>0.424605265353332</v>
       </c>
       <c r="G21">
-        <v>0.5955227668289209</v>
+        <v>0.3980097142317642</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.5697136128652364</v>
+        <v>0.3204598294937268</v>
       </c>
       <c r="C22">
-        <v>0.4538092986418497</v>
+        <v>0.2785680359787788</v>
       </c>
       <c r="D22">
-        <v>0.2196776215104349</v>
+        <v>0.2306258404797179</v>
       </c>
       <c r="E22">
-        <v>0.1533600503052278</v>
+        <v>0.2588043636512737</v>
       </c>
       <c r="F22">
-        <v>0.3612302884435364</v>
+        <v>0.424605265353332</v>
       </c>
       <c r="G22">
-        <v>0.2580910369955698</v>
+        <v>0.3980097142317642</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
-        <v>1.088537761783374</v>
+        <v>0.4212031081291395</v>
       </c>
       <c r="C23">
-        <v>0.5735180732958894</v>
+        <v>0.2037468715889071</v>
       </c>
       <c r="D23">
-        <v>0.961608923483921</v>
+        <v>0.3361597012975285</v>
       </c>
       <c r="E23">
-        <v>1.225367466927984</v>
+        <v>0.4405669464567136</v>
       </c>
       <c r="F23">
-        <v>1.138269230769236</v>
+        <v>0.5906946375756944</v>
       </c>
       <c r="G23">
-        <v>1.147987729214342</v>
+        <v>0.5573761304801144</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
-        <v>0.8004510921177566</v>
+        <v>0.4212031081291395</v>
       </c>
       <c r="C24">
-        <v>0.01061571125265402</v>
+        <v>0.2037468715889071</v>
       </c>
       <c r="D24">
-        <v>1.107754002648363</v>
+        <v>0.3361597012975285</v>
       </c>
       <c r="E24">
-        <v>1.458181982012431</v>
+        <v>0.4405669464567136</v>
       </c>
       <c r="F24">
-        <v>1.191514736442728</v>
+        <v>0.5906946375756944</v>
       </c>
       <c r="G24">
-        <v>1.305239166206532</v>
+        <v>0.5573761304801144</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.4227000427899048</v>
+        <v>0.2314027251885807</v>
       </c>
       <c r="C25">
-        <v>0.4549899096674994</v>
+        <v>0.1755525391359215</v>
       </c>
       <c r="D25">
-        <v>0.8739972899729066</v>
+        <v>0.2870604971907948</v>
       </c>
       <c r="E25">
-        <v>1.200867768595039</v>
+        <v>0.3857593755147237</v>
       </c>
       <c r="F25">
-        <v>0.6512090592334572</v>
+        <v>0.3926450869707452</v>
       </c>
       <c r="G25">
-        <v>0.8219821708282342</v>
+        <v>0.4162387221039412</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
-        <v>0.03739837398374005</v>
+        <v>0.2314027251885807</v>
       </c>
       <c r="C26">
-        <v>0.1934429207156478</v>
+        <v>0.1755525391359215</v>
       </c>
       <c r="D26">
-        <v>0.8961647936398941</v>
+        <v>0.2870604971907948</v>
       </c>
       <c r="E26">
-        <v>1.265495867768591</v>
+        <v>0.3857593755147237</v>
       </c>
       <c r="F26">
-        <v>0.3756629120136186</v>
+        <v>0.3926450869707452</v>
       </c>
       <c r="G26">
-        <v>0.6575291225504258</v>
+        <v>0.4162387221039412</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
-        <v>0.8684858002341316</v>
+        <v>0.4111037439928282</v>
       </c>
       <c r="C27">
-        <v>0.9013459832619916</v>
+        <v>0.3644236461962082</v>
       </c>
       <c r="D27">
-        <v>0.8124858428853279</v>
+        <v>0.3248888882955324</v>
       </c>
       <c r="E27">
-        <v>0.7726540906578282</v>
+        <v>0.3493363658555687</v>
       </c>
       <c r="F27">
-        <v>0.7555695972126655</v>
+        <v>0.4727193840945389</v>
       </c>
       <c r="G27">
-        <v>0.7057414103594334</v>
+        <v>0.443632334347796</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.616364973671029</v>
+        <v>0.4111037439928282</v>
       </c>
       <c r="C28">
-        <v>0.6022664455500317</v>
+        <v>0.3644236461962082</v>
       </c>
       <c r="D28">
-        <v>0.5456127943384335</v>
+        <v>0.3248888882955324</v>
       </c>
       <c r="E28">
-        <v>0.468129896494542</v>
+        <v>0.3493363658555687</v>
       </c>
       <c r="F28">
-        <v>0.6152156668309717</v>
+        <v>0.4727193840945389</v>
       </c>
       <c r="G28">
-        <v>0.4520751369731327</v>
+        <v>0.443632334347796</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
-        <v>-0.2199627796220964</v>
+        <v>-0.09953328995513258</v>
       </c>
       <c r="C29">
-        <v>-0.07389166506502601</v>
+        <v>-0.02812337589968883</v>
       </c>
       <c r="D29">
-        <v>0.1829652137217497</v>
+        <v>0.04831208920975597</v>
       </c>
       <c r="E29">
-        <v>0.1299078959235203</v>
+        <v>0.04751354253721017</v>
       </c>
       <c r="F29">
-        <v>-0.1336055205933237</v>
+        <v>-0.06902665614374838</v>
       </c>
       <c r="G29">
-        <v>-0.02348838966317501</v>
+        <v>-0.01306889032472195</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
-        <v>0.06091150733694803</v>
+        <v>-0.09953328995513258</v>
       </c>
       <c r="C30">
-        <v>0.1250152874797757</v>
+        <v>-0.02812337589968883</v>
       </c>
       <c r="D30">
-        <v>-0.0459965060161504</v>
+        <v>0.04831208920975597</v>
       </c>
       <c r="E30">
-        <v>0.01376829125898488</v>
+        <v>0.04751354253721017</v>
       </c>
       <c r="F30">
-        <v>-0.05875493411882184</v>
+        <v>-0.06902665614374838</v>
       </c>
       <c r="G30">
-        <v>-0.08010649247973618</v>
+        <v>-0.01306889032472195</v>
       </c>
     </row>
   </sheetData>
